--- a/Excel/EquipReformFeeConfig.xlsx
+++ b/Excel/EquipReformFeeConfig.xlsx
@@ -1125,10 +1125,10 @@
         <v>50</v>
       </c>
       <c r="F6" s="7">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G6" s="7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
@@ -1148,10 +1148,10 @@
       </c>
       <c r="F7" s="7">
         <f>F6+G6*(E6-D6)</f>
-        <v>59</v>
+        <v>2550</v>
       </c>
       <c r="G7" s="7">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
@@ -1171,10 +1171,10 @@
       </c>
       <c r="F8" s="7">
         <f>F7+G7*(E7-D7)</f>
-        <v>157</v>
+        <v>7450</v>
       </c>
       <c r="G8" s="7">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>

--- a/Excel/EquipReformFeeConfig.xlsx
+++ b/Excel/EquipReformFeeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
   <si>
     <t>Id</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>RiseFee</t>
+  </si>
+  <si>
+    <t>StoneFee</t>
   </si>
   <si>
     <t>int</t>
@@ -1033,11 +1036,11 @@
     <col min="3" max="3" width="6.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.125" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="6" max="8" width="13.625" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1045,8 +1048,9 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1054,8 +1058,9 @@
       <c r="E2" s="2"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1073,8 +1078,11 @@
       <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="H3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
@@ -1092,23 +1100,29 @@
       <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="H4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1130,6 +1144,9 @@
       <c r="G6" s="7">
         <v>50</v>
       </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
@@ -1140,18 +1157,21 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f>E6+1</f>
+        <f t="shared" ref="D7:D9" si="0">E6+1</f>
         <v>51</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
       </c>
       <c r="F7" s="7">
-        <f>F6+G6*(E6-D6)</f>
+        <f t="shared" ref="F7:F9" si="1">F6+G6*(E6-D6)</f>
         <v>2550</v>
       </c>
       <c r="G7" s="7">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="H7" s="7">
+        <v>2</v>
       </c>
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
@@ -1163,18 +1183,21 @@
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <f>E7+1</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="E8" s="2">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F8" s="7">
-        <f>F7+G7*(E7-D7)</f>
-        <v>7450</v>
+        <f t="shared" si="1"/>
+        <v>6225</v>
       </c>
       <c r="G8" s="7">
-        <v>150</v>
+        <v>100</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3</v>
       </c>
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
@@ -1182,11 +1205,26 @@
     <row r="9" customFormat="1" spans="1:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>151</v>
+      </c>
+      <c r="E9" s="2">
+        <v>200</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="1"/>
+        <v>11125</v>
+      </c>
+      <c r="G9" s="7">
+        <v>150</v>
+      </c>
+      <c r="H9" s="7">
+        <v>4</v>
+      </c>
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
@@ -1198,6 +1236,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
@@ -1209,6 +1248,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
@@ -1220,6 +1260,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
@@ -1231,6 +1272,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
@@ -1242,6 +1284,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
@@ -1253,6 +1296,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="7"/>
       <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
@@ -1264,6 +1308,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
@@ -1275,6 +1320,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
@@ -1286,6 +1332,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
@@ -1297,6 +1344,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
@@ -1308,6 +1356,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
@@ -1319,6 +1368,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
@@ -1330,6 +1380,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
@@ -1341,6 +1392,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
@@ -1352,6 +1404,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
@@ -1363,6 +1416,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
@@ -1374,12 +1428,13 @@
       <c r="E26" s="2"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
       <c r="XEQ26" s="2"/>
       <c r="XER26" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F2:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H4 H5 H2:H3 F2:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,F2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipReformFeeConfig.xlsx
+++ b/Excel/EquipReformFeeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1157,14 +1157,14 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D9" si="0">E6+1</f>
+        <f t="shared" ref="D7:D13" si="0">E6+1</f>
         <v>51</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" ref="F7:F9" si="1">F6+G6*(E6-D6)</f>
+        <f t="shared" ref="F7:F13" si="1">F6+G6*(E6-D6)</f>
         <v>2550</v>
       </c>
       <c r="G7" s="7">
@@ -1231,48 +1231,104 @@
     <row r="10" customFormat="1" spans="1:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>201</v>
+      </c>
+      <c r="E10" s="2">
+        <v>250</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="1"/>
+        <v>18475</v>
+      </c>
+      <c r="G10" s="7">
+        <v>200</v>
+      </c>
+      <c r="H10" s="7">
+        <v>5</v>
+      </c>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
     <row r="11" customFormat="1" spans="1:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>251</v>
+      </c>
+      <c r="E11" s="2">
+        <v>300</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="1"/>
+        <v>28275</v>
+      </c>
+      <c r="G11" s="7">
+        <v>250</v>
+      </c>
+      <c r="H11" s="7">
+        <v>6</v>
+      </c>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
     <row r="12" customFormat="1" spans="1:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="C12" s="2">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>301</v>
+      </c>
+      <c r="E12" s="2">
+        <v>400</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="1"/>
+        <v>40525</v>
+      </c>
+      <c r="G12" s="7">
+        <v>325</v>
+      </c>
+      <c r="H12" s="7">
+        <v>8</v>
+      </c>
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
     <row r="13" customFormat="1" spans="1:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="C13" s="2">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>401</v>
+      </c>
+      <c r="E13" s="2">
+        <v>500</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="1"/>
+        <v>72700</v>
+      </c>
+      <c r="G13" s="7">
+        <v>400</v>
+      </c>
+      <c r="H13" s="7">
+        <v>10</v>
+      </c>
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
@@ -1434,7 +1490,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H4 H5 H2:H3 F2:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F2:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,F2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipReformFeeConfig.xlsx
+++ b/Excel/EquipReformFeeConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t>Id</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>long</t>
+  </si>
+  <si>
+    <t>double</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1032,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XER26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
@@ -1060,7 +1063,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:8">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1082,7 +1085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:8">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
@@ -1104,7 +1107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
@@ -1117,16 +1120,16 @@
         <v>7</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:16372">
+    <row r="6" customFormat="1" ht="14" spans="1:16372">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1150,21 +1153,21 @@
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
-    <row r="7" customFormat="1" spans="1:16372">
+    <row r="7" customFormat="1" ht="14" spans="1:16372">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D13" si="0">E6+1</f>
+        <f t="shared" ref="D7:D16" si="0">E6+1</f>
         <v>51</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" ref="F7:F13" si="1">F6+G6*(E6-D6)</f>
+        <f t="shared" ref="F7:F16" si="1">F6+G6*(E6-D6)</f>
         <v>2550</v>
       </c>
       <c r="G7" s="7">
@@ -1176,7 +1179,7 @@
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
     </row>
-    <row r="8" customFormat="1" spans="1:16372">
+    <row r="8" customFormat="1" ht="14" spans="1:16372">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -1202,7 +1205,7 @@
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
     </row>
-    <row r="9" customFormat="1" spans="1:16372">
+    <row r="9" customFormat="1" ht="14" spans="1:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -1228,7 +1231,7 @@
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
-    <row r="10" customFormat="1" spans="1:16372">
+    <row r="10" customFormat="1" ht="14" spans="1:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -1254,7 +1257,7 @@
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
-    <row r="11" customFormat="1" spans="1:16372">
+    <row r="11" customFormat="1" ht="14" spans="1:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -1280,7 +1283,7 @@
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
-    <row r="12" customFormat="1" spans="1:16372">
+    <row r="12" customFormat="1" ht="14" spans="1:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -1306,7 +1309,7 @@
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
-    <row r="13" customFormat="1" spans="1:16372">
+    <row r="13" customFormat="1" ht="14" spans="1:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -1332,43 +1335,85 @@
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
-    <row r="14" customFormat="1" spans="1:16372">
+    <row r="14" customFormat="1" ht="14" spans="1:16372">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="C14" s="2">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>501</v>
+      </c>
+      <c r="E14" s="2">
+        <v>600</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="1"/>
+        <v>112300</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>15</v>
+      </c>
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
-    <row r="15" customFormat="1" spans="1:16372">
+    <row r="15" customFormat="1" ht="14" spans="1:16372">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>601</v>
+      </c>
+      <c r="E15" s="2">
+        <v>750</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="1"/>
+        <v>211300</v>
+      </c>
+      <c r="G15" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>20</v>
+      </c>
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
-    <row r="16" customFormat="1" spans="1:16372">
+    <row r="16" customFormat="1" ht="14" spans="1:16372">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>751</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="1"/>
+        <v>658300</v>
+      </c>
+      <c r="G16" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>25</v>
+      </c>
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
-    <row r="17" customFormat="1" spans="1:16372">
+    <row r="17" customFormat="1" ht="14" spans="1:16372">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1380,7 +1425,7 @@
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
-    <row r="18" customFormat="1" spans="1:16372">
+    <row r="18" customFormat="1" ht="14" spans="1:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1392,7 +1437,7 @@
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
-    <row r="19" customFormat="1" spans="1:16372">
+    <row r="19" customFormat="1" ht="14" spans="1:16372">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1404,7 +1449,7 @@
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
-    <row r="20" customFormat="1" spans="1:16372">
+    <row r="20" customFormat="1" ht="14" spans="1:16372">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1416,7 +1461,7 @@
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
-    <row r="21" customFormat="1" spans="1:16372">
+    <row r="21" customFormat="1" ht="14" spans="1:16372">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1428,7 +1473,7 @@
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
-    <row r="22" customFormat="1" spans="1:16372">
+    <row r="22" customFormat="1" ht="14" spans="1:16372">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1440,7 +1485,7 @@
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
-    <row r="23" customFormat="1" spans="1:16372">
+    <row r="23" customFormat="1" ht="14" spans="1:16372">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1452,7 +1497,7 @@
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
-    <row r="24" customFormat="1" spans="1:16372">
+    <row r="24" customFormat="1" ht="14" spans="1:16372">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1464,7 +1509,7 @@
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
-    <row r="25" customFormat="1" spans="1:16372">
+    <row r="25" customFormat="1" ht="14" spans="1:16372">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1476,7 +1521,7 @@
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
-    <row r="26" customFormat="1" spans="1:16372">
+    <row r="26" customFormat="1" ht="14" spans="1:16372">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>

--- a/Excel/EquipReformFeeConfig.xlsx
+++ b/Excel/EquipReformFeeConfig.xlsx
@@ -1043,7 +1043,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:8 16371:16372">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1053,7 +1053,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+    <row r="2" s="1" customFormat="1" spans="1:8 16371:16372">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1063,7 +1063,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:8 16371:16372">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1085,7 +1085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:8 16371:16372">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
@@ -1107,7 +1107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:8 16371:16372">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
@@ -1129,7 +1129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="14" spans="1:16372">
+    <row r="6" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1153,21 +1153,21 @@
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
-    <row r="7" customFormat="1" ht="14" spans="1:16372">
+    <row r="7" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D16" si="0">E6+1</f>
+        <f t="shared" ref="D7:D17" si="0">E6+1</f>
         <v>51</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" ref="F7:F16" si="1">F6+G6*(E6-D6)</f>
+        <f t="shared" ref="F7:F17" si="1">F6+G6*(E6-D6)</f>
         <v>2550</v>
       </c>
       <c r="G7" s="7">
@@ -1179,7 +1179,7 @@
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
     </row>
-    <row r="8" customFormat="1" ht="14" spans="1:16372">
+    <row r="8" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -1205,7 +1205,7 @@
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
     </row>
-    <row r="9" customFormat="1" ht="14" spans="1:16372">
+    <row r="9" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -1231,7 +1231,7 @@
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
-    <row r="10" customFormat="1" ht="14" spans="1:16372">
+    <row r="10" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -1257,7 +1257,7 @@
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
-    <row r="11" customFormat="1" ht="14" spans="1:16372">
+    <row r="11" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -1283,7 +1283,7 @@
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
-    <row r="12" customFormat="1" ht="14" spans="1:16372">
+    <row r="12" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -1309,7 +1309,7 @@
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
-    <row r="13" customFormat="1" ht="14" spans="1:16372">
+    <row r="13" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -1335,7 +1335,7 @@
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
-    <row r="14" customFormat="1" ht="14" spans="1:16372">
+    <row r="14" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2">
@@ -1361,7 +1361,7 @@
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
-    <row r="15" customFormat="1" ht="14" spans="1:16372">
+    <row r="15" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2">
@@ -1387,7 +1387,7 @@
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
-    <row r="16" customFormat="1" ht="14" spans="1:16372">
+    <row r="16" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2">
@@ -1413,19 +1413,33 @@
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
-    <row r="17" customFormat="1" ht="14" spans="1:16372">
+    <row r="17" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1200</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="1"/>
+        <v>2152300</v>
+      </c>
+      <c r="G17" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>35</v>
+      </c>
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
-    <row r="18" customFormat="1" ht="14" spans="1:16372">
+    <row r="18" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1437,7 +1451,7 @@
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
-    <row r="19" customFormat="1" ht="14" spans="1:16372">
+    <row r="19" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1449,7 +1463,7 @@
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
-    <row r="20" customFormat="1" ht="14" spans="1:16372">
+    <row r="20" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1461,7 +1475,7 @@
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
-    <row r="21" customFormat="1" ht="14" spans="1:16372">
+    <row r="21" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1473,7 +1487,7 @@
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
-    <row r="22" customFormat="1" ht="14" spans="1:16372">
+    <row r="22" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1485,7 +1499,7 @@
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
-    <row r="23" customFormat="1" ht="14" spans="1:16372">
+    <row r="23" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1497,7 +1511,7 @@
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
-    <row r="24" customFormat="1" ht="14" spans="1:16372">
+    <row r="24" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1509,7 +1523,7 @@
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
-    <row r="25" customFormat="1" ht="14" spans="1:16372">
+    <row r="25" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1521,7 +1535,7 @@
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
-    <row r="26" customFormat="1" ht="14" spans="1:16372">
+    <row r="26" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>

--- a/Excel/EquipReformFeeConfig.xlsx
+++ b/Excel/EquipReformFeeConfig.xlsx
@@ -1160,14 +1160,14 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D17" si="0">E6+1</f>
+        <f t="shared" ref="D7:D18" si="0">E6+1</f>
         <v>51</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" ref="F7:F17" si="1">F6+G6*(E6-D6)</f>
+        <f t="shared" ref="F7:F18" si="1">F6+G6*(E6-D6)</f>
         <v>2550</v>
       </c>
       <c r="G7" s="7">
@@ -1442,12 +1442,26 @@
     <row r="18" customFormat="1" ht="14" spans="1:8 16371:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="C18" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>1201</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1500</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="1"/>
+        <v>3943300</v>
+      </c>
+      <c r="G18" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>50</v>
+      </c>
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
